--- a/Data/OM/OM_Quizzes.xlsx
+++ b/Data/OM/OM_Quizzes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyCode\mba\Data\Semester 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyCode\mba_quiz\Data\OM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21ADC1D-A3C1-4DD6-8227-0DDC85D4FF88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46FFF869-3F88-4323-819B-93EC1385C00F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="4" activeTab="11" xr2:uid="{850D3C83-EED4-4016-BDB5-EF8EECDCB418}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{850D3C83-EED4-4016-BDB5-EF8EECDCB418}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="13" r:id="rId1"/>
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1512" uniqueCount="1116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="1118">
   <si>
     <t xml:space="preserve">Question 1 </t>
   </si>
@@ -3453,6 +3453,12 @@
   </si>
   <si>
     <t>37</t>
+  </si>
+  <si>
+    <t>Answer</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
 </sst>
 </file>
@@ -3546,14 +3552,15 @@
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="1" xr16:uid="{325CFB99-2D68-46FA-9451-0C1E2AD2B49E}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3561,14 +3568,15 @@
 
 <file path=xl/queryTables/queryTable10.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_10" connectionId="2" xr16:uid="{BEFABE85-0BA0-40D9-A91E-B5B91A1A4B5F}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3576,14 +3584,15 @@
 
 <file path=xl/queryTables/queryTable11.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_11" connectionId="3" xr16:uid="{1AD50F50-3783-410F-9DCB-7285539C6984}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3591,14 +3600,15 @@
 
 <file path=xl/queryTables/queryTable12.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_12" connectionId="4" xr16:uid="{35073DD3-9CBC-4F83-80E5-4489E5753BCC}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3606,14 +3616,15 @@
 
 <file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_2" connectionId="5" xr16:uid="{97F99454-AEA9-40B2-8617-EDB88FC2CD7F}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3621,14 +3632,15 @@
 
 <file path=xl/queryTables/queryTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_3" connectionId="6" xr16:uid="{E5AEC814-9DAD-4C40-85DA-47A320C82431}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3636,14 +3648,15 @@
 
 <file path=xl/queryTables/queryTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_4" connectionId="7" xr16:uid="{150264A7-33A9-4DDB-92F7-AB092D2C167C}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3651,14 +3664,15 @@
 
 <file path=xl/queryTables/queryTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_5" connectionId="8" xr16:uid="{0C30A7B5-BE3D-48E4-A00E-F3A3449D3F75}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3666,14 +3680,15 @@
 
 <file path=xl/queryTables/queryTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_6" connectionId="9" xr16:uid="{FDEB5CB8-828E-4AB2-8A77-59B97A094027}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3681,14 +3696,15 @@
 
 <file path=xl/queryTables/queryTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_7" connectionId="10" xr16:uid="{657D26A9-1BA7-4563-8B90-D09A327AB14B}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3696,14 +3712,15 @@
 
 <file path=xl/queryTables/queryTable8.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_8" connectionId="11" xr16:uid="{E7128950-AD9A-406D-A89F-6ABE3A935F97}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3711,194 +3728,207 @@
 
 <file path=xl/queryTables/queryTable9.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_9" connectionId="12" xr16:uid="{A735C944-2A51-470D-9FB7-711B8AF5409D}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{6DAA7E45-1438-48E4-BBD4-3FF9A64650B6}" name="Invoked_Function" displayName="Invoked_Function" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{6DAA7E45-1438-48E4-BBD4-3FF9A64650B6}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{4F4DC1AE-9891-4D2C-81CA-FF83A0666932}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{6DAA7E45-1438-48E4-BBD4-3FF9A64650B6}" name="Invoked_Function" displayName="Invoked_Function" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{6DAA7E45-1438-48E4-BBD4-3FF9A64650B6}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{4F4DC1AE-9891-4D2C-81CA-FF83A0666932}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{3316EEB5-4012-4932-949C-59C1B8B3015E}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{F7253B9B-F333-458E-BEBB-53DA19583134}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{74EA87A1-A1E1-4D42-B81A-0036004754E0}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{2D97CB92-4337-4203-8972-331AF51189E0}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{E1354C7B-1809-4560-8951-4DD5C0DC2C16}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{6FE83A22-6E03-4CF1-AA1C-101BDBC81BB3}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{435052D4-19AB-4E15-8BAC-29CC5B7F9B71}" name="Invoked_Function__10" displayName="Invoked_Function__10" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{435052D4-19AB-4E15-8BAC-29CC5B7F9B71}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{088F530A-F6B0-4576-8DAF-939017B752F3}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{435052D4-19AB-4E15-8BAC-29CC5B7F9B71}" name="Invoked_Function__10" displayName="Invoked_Function__10" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{435052D4-19AB-4E15-8BAC-29CC5B7F9B71}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{088F530A-F6B0-4576-8DAF-939017B752F3}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{98FBB0FF-3819-418D-AE51-83B0880EA881}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{041B5EC7-E505-4A80-97E7-5D2D58BC4D57}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{5C0441B3-7FEC-4475-803C-74BE6EE3530C}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{0177DFC1-92EF-4147-9B64-614BFC2865A6}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{9CA78E9E-2FD7-4C89-8824-1038EB6122E5}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{B890E260-0D99-403F-BF4A-C5A7A722C38E}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{2EFC25D6-673F-46F4-8772-BA41AC6386EF}" name="Invoked_Function__11" displayName="Invoked_Function__11" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{2EFC25D6-673F-46F4-8772-BA41AC6386EF}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{D5716560-84A7-4D1E-87A8-12FC230551F4}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{2EFC25D6-673F-46F4-8772-BA41AC6386EF}" name="Invoked_Function__11" displayName="Invoked_Function__11" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{2EFC25D6-673F-46F4-8772-BA41AC6386EF}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{D5716560-84A7-4D1E-87A8-12FC230551F4}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{6DCE77D5-DFC2-4749-93EB-7E66318B6086}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{6C44B63C-AFA2-4A05-8864-468ECE1608C7}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{811FFC1A-E1FB-4C61-A29D-211B566B1358}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{1BDF77CB-CE89-4CDB-9B3D-E41F0FCCA607}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{220C9FCF-3520-4359-9D31-BEDE7E8A53A6}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{02692A2F-4095-4B0F-8EC6-F5794DFFC120}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{54349323-E225-4000-80BB-229C42209659}" name="Invoked_Function__12" displayName="Invoked_Function__12" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{54349323-E225-4000-80BB-229C42209659}"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{54349323-E225-4000-80BB-229C42209659}" name="Invoked_Function__12" displayName="Invoked_Function__12" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{54349323-E225-4000-80BB-229C42209659}"/>
+  <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{34D2D8E0-5D98-4E33-9B27-4EB54DF9D0DD}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{6D013BCE-29CA-480A-856D-4B77441E48A5}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{65878C6D-02B2-4718-8E1A-2EA522FAB55C}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{FCB25CD2-1B15-4356-AE5A-1C374BFC8E60}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{C988A504-8CB5-4F63-A371-88C0FA7019C6}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{D87706B8-99E8-4A1F-BD8F-531AD67222B6}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{21847782-CF1A-4757-8DE0-5E5D81F11A92}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{C3BA8602-D9EC-4CC6-8342-A610BF185308}" name="Invoked_Function__2" displayName="Invoked_Function__2" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{C3BA8602-D9EC-4CC6-8342-A610BF185308}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{FD297B3E-6F4E-4299-BC61-F59EB049387C}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="1"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{C3BA8602-D9EC-4CC6-8342-A610BF185308}" name="Invoked_Function__2" displayName="Invoked_Function__2" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{C3BA8602-D9EC-4CC6-8342-A610BF185308}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{FD297B3E-6F4E-4299-BC61-F59EB049387C}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{08808285-7BB7-4B8E-B6A2-862AFC142B9D}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{8E1D4074-7785-4456-8080-9517A54670F4}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{DAABEC48-0663-457E-9A87-F652A956CBC8}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{FD791412-8E87-45D1-A0F0-5C8E354E34AB}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{AEEE58EE-27FA-4530-AE7E-449D138856F3}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{EA330D24-3690-4066-8909-014ECE8EEDB1}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{3ABD55B9-6434-45DD-B30C-BEA19CF6D4E9}" name="Invoked_Function__3" displayName="Invoked_Function__3" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{3ABD55B9-6434-45DD-B30C-BEA19CF6D4E9}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{6ED9E7E7-904D-44A8-922A-0AE2929493CB}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{3ABD55B9-6434-45DD-B30C-BEA19CF6D4E9}" name="Invoked_Function__3" displayName="Invoked_Function__3" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{3ABD55B9-6434-45DD-B30C-BEA19CF6D4E9}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{6ED9E7E7-904D-44A8-922A-0AE2929493CB}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{FFFA1420-5284-4BAA-BDB5-2419CBBC7713}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{B4B389E9-32FC-4116-AD66-165CF95D0CF5}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{71E5AE82-4D16-417D-BC33-5D8339BD7813}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{0DC00FD5-B39C-4C7D-80D4-BE478A7ECACE}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{77E94589-F0B8-4A44-80BB-DAE8979EC75B}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{F47C8465-2E80-459B-B7D9-255E2FCFD2BE}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{F391CFF9-11B6-4C6A-B49E-E899846B77FB}" name="Invoked_Function__4" displayName="Invoked_Function__4" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{F391CFF9-11B6-4C6A-B49E-E899846B77FB}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{6E57B712-A176-4715-93AA-F697952F56E8}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{F391CFF9-11B6-4C6A-B49E-E899846B77FB}" name="Invoked_Function__4" displayName="Invoked_Function__4" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{F391CFF9-11B6-4C6A-B49E-E899846B77FB}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{6E57B712-A176-4715-93AA-F697952F56E8}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{2FFB4E15-CDF9-4C3B-8950-6C99A84E5DBF}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{E31F55BB-5175-425B-9F71-96B4049ABBD7}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{6A1D1FF4-DC71-4C35-82EC-9C40D5D74293}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{F7165553-919D-4942-AB59-5528FC159CAE}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{5DD93BD7-5A05-4951-95A9-07CE12BAB2F1}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{DC15873A-C9CB-43E8-8D3B-42BE5DBBA008}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{0B336DAA-9B7B-4435-8098-7BE4D3C2A28B}" name="Invoked_Function__5" displayName="Invoked_Function__5" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{0B336DAA-9B7B-4435-8098-7BE4D3C2A28B}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{6F04D2E1-D13A-4CCE-BC1C-2683E408F03A}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{0B336DAA-9B7B-4435-8098-7BE4D3C2A28B}" name="Invoked_Function__5" displayName="Invoked_Function__5" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{0B336DAA-9B7B-4435-8098-7BE4D3C2A28B}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{6F04D2E1-D13A-4CCE-BC1C-2683E408F03A}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{76CE457E-A45B-4F93-A927-93D8237A9E97}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{F6D6C614-E9E1-4658-A7BE-C0656F92C0EB}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{21D96AD7-C064-4EBE-A1BC-88EFADE23288}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{7439075B-50E8-46A4-B437-827CCFD92887}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{A346E2EB-6DCF-438F-918A-B7E83DEF04D8}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{C8D1B2AE-BA0E-4F91-BAED-46351473388B}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{976449B6-5F63-4BCD-ADE8-D8DB40B8FA4C}" name="Invoked_Function__6" displayName="Invoked_Function__6" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{976449B6-5F63-4BCD-ADE8-D8DB40B8FA4C}"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{976449B6-5F63-4BCD-ADE8-D8DB40B8FA4C}" name="Invoked_Function__6" displayName="Invoked_Function__6" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{976449B6-5F63-4BCD-ADE8-D8DB40B8FA4C}"/>
+  <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{145C51E1-C78B-47CB-A5AC-DDA65C8E18A2}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{E51CC0F5-CCB1-472B-BD8C-7D6D83E4CF15}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{D195B80E-4918-401A-B38D-F722EFAFE08F}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{4D3E205A-4061-4184-85E4-520B5613029F}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{8C000D3B-F519-45AD-9459-388902A7C115}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{5B510EE2-B36F-4149-BD6B-0EC5958C6DF4}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{3C49B272-B608-4316-9B23-93B880634A48}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{6C35EC66-EE0E-4044-BDBC-3336C63ABAA5}" name="Invoked_Function__7" displayName="Invoked_Function__7" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{6C35EC66-EE0E-4044-BDBC-3336C63ABAA5}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{204FFCFE-E32A-4180-A147-D0D393037A11}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{6C35EC66-EE0E-4044-BDBC-3336C63ABAA5}" name="Invoked_Function__7" displayName="Invoked_Function__7" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{6C35EC66-EE0E-4044-BDBC-3336C63ABAA5}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{204FFCFE-E32A-4180-A147-D0D393037A11}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{2117BA69-A095-45E8-85BC-A8FF775648B7}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{E33BD793-75DE-4B42-B115-CFC63E7EA719}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{FEBB3995-9725-44AA-81F2-F9F10A434981}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{6252131D-3B78-4FC3-BC7D-FCC06A2E9231}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{16F4EB75-9BE6-4D65-872C-E546005C5586}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{423BDAEE-13D5-45C1-84C8-A18301E451D2}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{58941E16-4E46-41BD-B8E1-D1E32BB562A5}" name="Invoked_Function__8" displayName="Invoked_Function__8" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{58941E16-4E46-41BD-B8E1-D1E32BB562A5}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{985D7F0A-A4BA-43C5-A78F-3ECA5F83658D}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{58941E16-4E46-41BD-B8E1-D1E32BB562A5}" name="Invoked_Function__8" displayName="Invoked_Function__8" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{58941E16-4E46-41BD-B8E1-D1E32BB562A5}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{985D7F0A-A4BA-43C5-A78F-3ECA5F83658D}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{E44469FE-6E9E-4B34-86C1-1E0F50A5BB56}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{C056C849-CF48-45C1-8A39-78AB9AA074F7}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{DAA2F508-B0CD-422E-BC72-CA367389D287}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{5CB77123-0C1F-43F9-9E0E-06383F61317F}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{C3A03102-4D2A-4616-9E80-6353826666BF}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{90D5ABC6-53DA-47B9-8F16-DE6B06A77DE2}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{20220D49-688A-4E6F-B076-C476A008EA2E}" name="Invoked_Function__9" displayName="Invoked_Function__9" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{20220D49-688A-4E6F-B076-C476A008EA2E}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{9CBF8650-ACEB-4018-BE8E-BBA77FDBEDB5}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{20220D49-688A-4E6F-B076-C476A008EA2E}" name="Invoked_Function__9" displayName="Invoked_Function__9" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{20220D49-688A-4E6F-B076-C476A008EA2E}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{9CBF8650-ACEB-4018-BE8E-BBA77FDBEDB5}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{DFF65E6F-2820-4C06-BF88-2E5AEA27798D}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{2DA3D069-C9DB-4141-AAC7-0DD1B471C96D}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{E692B638-331D-4457-A25B-4FCECAF8D4C0}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{C97853C9-A286-4248-A5C1-ECDB66AA5880}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{C5D677EB-B477-461C-9364-1AB51ED8BBEA}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{049E7FDE-E31D-420B-BECC-51860B67442D}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4222,7 +4252,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B40EA3F6-8028-4DB6-991A-73C6F4E6DD39}">
   <sheetPr codeName="Sheet24"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -4233,7 +4263,7 @@
     <col min="6" max="6" width="69.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1094</v>
       </c>
@@ -4252,8 +4282,11 @@
       <c r="F1" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -4272,8 +4305,11 @@
       <c r="F2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -4292,8 +4328,11 @@
       <c r="F3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -4312,8 +4351,11 @@
       <c r="F4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -4332,8 +4374,11 @@
       <c r="F5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -4352,8 +4397,11 @@
       <c r="F6" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -4372,8 +4420,11 @@
       <c r="F7" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -4392,8 +4443,11 @@
       <c r="F8" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -4412,8 +4466,11 @@
       <c r="F9" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -4432,8 +4489,11 @@
       <c r="F10" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -4452,8 +4512,11 @@
       <c r="F11" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -4472,8 +4535,11 @@
       <c r="F12" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -4492,8 +4558,11 @@
       <c r="F13" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -4512,8 +4581,11 @@
       <c r="F14" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>75</v>
       </c>
@@ -4532,8 +4604,11 @@
       <c r="F15" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -4552,8 +4627,11 @@
       <c r="F16" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -4572,8 +4650,11 @@
       <c r="F17" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>93</v>
       </c>
@@ -4592,8 +4673,11 @@
       <c r="F18" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -4612,8 +4696,11 @@
       <c r="F19" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -4632,8 +4719,11 @@
       <c r="F20" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -4651,6 +4741,9 @@
       </c>
       <c r="F21" t="s">
         <v>114</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1117</v>
       </c>
     </row>
   </sheetData>
@@ -4664,7 +4757,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B5376FF-441B-4D4D-A1F8-2A985050469E}">
   <sheetPr codeName="Sheet15"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -4675,7 +4768,7 @@
     <col min="6" max="6" width="30.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1094</v>
       </c>
@@ -4694,8 +4787,11 @@
       <c r="F1" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -4714,8 +4810,11 @@
       <c r="F2" t="s">
         <v>835</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -4734,8 +4833,11 @@
       <c r="F3" t="s">
         <v>840</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -4754,8 +4856,11 @@
       <c r="F4" t="s">
         <v>845</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -4774,8 +4879,11 @@
       <c r="F5" t="s">
         <v>850</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -4794,8 +4902,11 @@
       <c r="F6" t="s">
         <v>855</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -4814,8 +4925,11 @@
       <c r="F7" t="s">
         <v>860</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -4834,8 +4948,11 @@
       <c r="F8" t="s">
         <v>865</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -4854,8 +4971,11 @@
       <c r="F9" t="s">
         <v>870</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -4874,8 +4994,11 @@
       <c r="F10" t="s">
         <v>875</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -4894,8 +5017,11 @@
       <c r="F11" t="s">
         <v>880</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -4914,8 +5040,11 @@
       <c r="F12" t="s">
         <v>885</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -4934,8 +5063,11 @@
       <c r="F13" t="s">
         <v>890</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -4954,8 +5086,11 @@
       <c r="F14" t="s">
         <v>895</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>75</v>
       </c>
@@ -4974,8 +5109,11 @@
       <c r="F15" t="s">
         <v>900</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -4994,8 +5132,11 @@
       <c r="F16" t="s">
         <v>905</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -5014,8 +5155,11 @@
       <c r="F17" t="s">
         <v>910</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>93</v>
       </c>
@@ -5034,8 +5178,11 @@
       <c r="F18" t="s">
         <v>915</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -5054,8 +5201,11 @@
       <c r="F19" t="s">
         <v>920</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -5074,8 +5224,11 @@
       <c r="F20" t="s">
         <v>879</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -5093,6 +5246,9 @@
       </c>
       <c r="F21" t="s">
         <v>925</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1117</v>
       </c>
     </row>
   </sheetData>
@@ -5106,7 +5262,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAAF5B06-1E11-459F-A6AF-D5A69891E2FB}">
   <sheetPr codeName="Sheet14"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -5117,7 +5273,7 @@
     <col min="6" max="6" width="42.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1094</v>
       </c>
@@ -5136,8 +5292,11 @@
       <c r="F1" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -5156,8 +5315,11 @@
       <c r="F2" t="s">
         <v>930</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -5176,8 +5338,11 @@
       <c r="F3" t="s">
         <v>934</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -5196,8 +5361,11 @@
       <c r="F4" t="s">
         <v>938</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -5216,8 +5384,11 @@
       <c r="F5" t="s">
         <v>942</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -5236,8 +5407,11 @@
       <c r="F6" t="s">
         <v>947</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -5256,8 +5430,11 @@
       <c r="F7" t="s">
         <v>951</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -5276,8 +5453,11 @@
       <c r="F8" t="s">
         <v>954</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -5296,8 +5476,11 @@
       <c r="F9" t="s">
         <v>959</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -5316,8 +5499,11 @@
       <c r="F10" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -5336,8 +5522,11 @@
       <c r="F11" t="s">
         <v>969</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -5356,8 +5545,11 @@
       <c r="F12" t="s">
         <v>973</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -5376,8 +5568,11 @@
       <c r="F13" t="s">
         <v>978</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -5396,8 +5591,11 @@
       <c r="F14" t="s">
         <v>983</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>75</v>
       </c>
@@ -5416,8 +5614,11 @@
       <c r="F15" t="s">
         <v>987</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -5436,8 +5637,11 @@
       <c r="F16" t="s">
         <v>992</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -5456,8 +5660,11 @@
       <c r="F17" t="s">
         <v>996</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>93</v>
       </c>
@@ -5476,8 +5683,11 @@
       <c r="F18" t="s">
         <v>1109</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -5496,8 +5706,11 @@
       <c r="F19" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -5516,8 +5729,11 @@
       <c r="F20" t="s">
         <v>1009</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -5535,6 +5751,9 @@
       </c>
       <c r="F21" t="s">
         <v>1014</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1117</v>
       </c>
     </row>
   </sheetData>
@@ -5548,7 +5767,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{866B9831-EA98-4EC6-B38A-C8A02C14EC71}">
   <sheetPr codeName="Sheet13"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -5559,7 +5778,7 @@
     <col min="6" max="6" width="24.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1094</v>
       </c>
@@ -5578,8 +5797,11 @@
       <c r="F1" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -5598,8 +5820,11 @@
       <c r="F2" t="s">
         <v>1018</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -5618,8 +5843,11 @@
       <c r="F3" t="s">
         <v>1023</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -5638,8 +5866,11 @@
       <c r="F4" t="s">
         <v>1028</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -5658,8 +5889,11 @@
       <c r="F5" t="s">
         <v>1033</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -5678,8 +5912,11 @@
       <c r="F6" t="s">
         <v>1038</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -5698,8 +5935,11 @@
       <c r="F7" t="s">
         <v>1043</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -5718,8 +5958,11 @@
       <c r="F8" t="s">
         <v>1048</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -5738,8 +5981,11 @@
       <c r="F9" t="s">
         <v>1028</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -5758,8 +6004,11 @@
       <c r="F10" t="s">
         <v>1054</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -5778,8 +6027,11 @@
       <c r="F11" t="s">
         <v>1059</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -5798,8 +6050,11 @@
       <c r="F12" t="s">
         <v>1064</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -5818,8 +6073,11 @@
       <c r="F13" t="s">
         <v>1069</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -5838,8 +6096,11 @@
       <c r="F14" t="s">
         <v>1028</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>75</v>
       </c>
@@ -5858,8 +6119,11 @@
       <c r="F15" t="s">
         <v>1075</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -5878,8 +6142,11 @@
       <c r="F16" t="s">
         <v>1080</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -5898,8 +6165,11 @@
       <c r="F17" t="s">
         <v>1021</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>93</v>
       </c>
@@ -5918,8 +6188,11 @@
       <c r="F18" t="s">
         <v>1053</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -5938,8 +6211,11 @@
       <c r="F19" t="s">
         <v>1089</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -5958,8 +6234,11 @@
       <c r="F20" t="s">
         <v>1091</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -5977,6 +6256,9 @@
       </c>
       <c r="F21" t="s">
         <v>1075</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1117</v>
       </c>
     </row>
   </sheetData>
@@ -5990,7 +6272,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AA81EB0-8CC8-4506-BB20-D07866F3254A}">
   <sheetPr codeName="Sheet23"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -6001,7 +6283,7 @@
     <col min="6" max="6" width="31.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1094</v>
       </c>
@@ -6020,8 +6302,11 @@
       <c r="F1" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -6040,8 +6325,11 @@
       <c r="F2" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -6060,8 +6348,11 @@
       <c r="F3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -6080,8 +6371,11 @@
       <c r="F4" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -6100,8 +6394,11 @@
       <c r="F5" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -6120,8 +6417,11 @@
       <c r="F6" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -6140,8 +6440,11 @@
       <c r="F7" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -6160,8 +6463,11 @@
       <c r="F8" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -6180,8 +6486,11 @@
       <c r="F9" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -6200,8 +6509,11 @@
       <c r="F10" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -6220,8 +6532,11 @@
       <c r="F11" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -6240,8 +6555,11 @@
       <c r="F12" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -6260,8 +6578,11 @@
       <c r="F13" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -6280,8 +6601,11 @@
       <c r="F14" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>75</v>
       </c>
@@ -6300,8 +6624,11 @@
       <c r="F15" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -6320,8 +6647,11 @@
       <c r="F16" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -6340,8 +6670,11 @@
       <c r="F17" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>93</v>
       </c>
@@ -6360,8 +6693,11 @@
       <c r="F18" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -6380,8 +6716,11 @@
       <c r="F19" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -6400,8 +6739,11 @@
       <c r="F20" t="s">
         <v>1113</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -6419,6 +6761,9 @@
       </c>
       <c r="F21" t="s">
         <v>1111</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1117</v>
       </c>
     </row>
   </sheetData>
@@ -6432,7 +6777,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9F31EC0-C492-4FC0-8063-B345F39B3341}">
   <sheetPr codeName="Sheet22"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -6443,7 +6788,7 @@
     <col min="6" max="6" width="50.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1094</v>
       </c>
@@ -6462,8 +6807,11 @@
       <c r="F1" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -6482,8 +6830,11 @@
       <c r="F2" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -6502,8 +6853,11 @@
       <c r="F3" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -6522,8 +6876,11 @@
       <c r="F4" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -6542,8 +6899,11 @@
       <c r="F5" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -6562,8 +6922,11 @@
       <c r="F6" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -6582,8 +6945,11 @@
       <c r="F7" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -6602,8 +6968,11 @@
       <c r="F8" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -6622,8 +6991,11 @@
       <c r="F9" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -6642,8 +7014,11 @@
       <c r="F10" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -6662,8 +7037,11 @@
       <c r="F11" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -6682,8 +7060,11 @@
       <c r="F12" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -6702,8 +7083,11 @@
       <c r="F13" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -6722,8 +7106,11 @@
       <c r="F14" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>75</v>
       </c>
@@ -6742,8 +7129,11 @@
       <c r="F15" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -6762,8 +7152,11 @@
       <c r="F16" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -6782,8 +7175,11 @@
       <c r="F17" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>93</v>
       </c>
@@ -6802,8 +7198,11 @@
       <c r="F18" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -6822,8 +7221,11 @@
       <c r="F19" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -6842,8 +7244,11 @@
       <c r="F20" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -6861,6 +7266,9 @@
       </c>
       <c r="F21" t="s">
         <v>281</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1117</v>
       </c>
     </row>
   </sheetData>
@@ -6874,7 +7282,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F219DC98-3EB6-4AEF-ACE3-B0B2E088B4E6}">
   <sheetPr codeName="Sheet21"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -6885,7 +7293,7 @@
     <col min="6" max="6" width="61.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1094</v>
       </c>
@@ -6904,8 +7312,11 @@
       <c r="F1" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -6924,8 +7335,11 @@
       <c r="F2" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -6944,8 +7358,11 @@
       <c r="F3" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -6964,8 +7381,11 @@
       <c r="F4" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -6984,8 +7404,11 @@
       <c r="F5" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -7004,8 +7427,11 @@
       <c r="F6" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -7024,8 +7450,11 @@
       <c r="F7" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -7044,8 +7473,11 @@
       <c r="F8" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -7064,8 +7496,11 @@
       <c r="F9" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -7084,8 +7519,11 @@
       <c r="F10" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -7104,8 +7542,11 @@
       <c r="F11" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -7124,8 +7565,11 @@
       <c r="F12" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -7144,8 +7588,11 @@
       <c r="F13" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -7164,8 +7611,11 @@
       <c r="F14" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>75</v>
       </c>
@@ -7184,8 +7634,11 @@
       <c r="F15" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -7204,8 +7657,11 @@
       <c r="F16" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -7224,8 +7680,11 @@
       <c r="F17" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>93</v>
       </c>
@@ -7244,8 +7703,11 @@
       <c r="F18" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -7264,8 +7726,11 @@
       <c r="F19" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -7284,8 +7749,11 @@
       <c r="F20" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -7303,6 +7771,9 @@
       </c>
       <c r="F21" t="s">
         <v>356</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1117</v>
       </c>
     </row>
   </sheetData>
@@ -7316,7 +7787,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04FFEB01-ECDF-4DC4-BA81-9F9AA3E964AE}">
   <sheetPr codeName="Sheet20"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -7327,7 +7798,7 @@
     <col min="6" max="6" width="66.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1094</v>
       </c>
@@ -7346,8 +7817,11 @@
       <c r="F1" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -7366,8 +7840,11 @@
       <c r="F2" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -7386,8 +7863,11 @@
       <c r="F3" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -7406,8 +7886,11 @@
       <c r="F4" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -7426,8 +7909,11 @@
       <c r="F5" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -7446,8 +7932,11 @@
       <c r="F6" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -7466,8 +7955,11 @@
       <c r="F7" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -7486,8 +7978,11 @@
       <c r="F8" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -7506,8 +8001,11 @@
       <c r="F9" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -7526,8 +8024,11 @@
       <c r="F10" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -7546,8 +8047,11 @@
       <c r="F11" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -7566,8 +8070,11 @@
       <c r="F12" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -7586,8 +8093,11 @@
       <c r="F13" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -7606,8 +8116,11 @@
       <c r="F14" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>75</v>
       </c>
@@ -7626,8 +8139,11 @@
       <c r="F15" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -7646,8 +8162,11 @@
       <c r="F16" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -7666,8 +8185,11 @@
       <c r="F17" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>93</v>
       </c>
@@ -7686,8 +8208,11 @@
       <c r="F18" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -7706,8 +8231,11 @@
       <c r="F19" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -7726,8 +8254,11 @@
       <c r="F20" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -7745,6 +8276,9 @@
       </c>
       <c r="F21" t="s">
         <v>457</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1117</v>
       </c>
     </row>
   </sheetData>
@@ -7758,7 +8292,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E38D906-345D-4A3F-8C59-FAC4B16ADBA8}">
   <sheetPr codeName="Sheet19"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -7769,7 +8303,7 @@
     <col min="6" max="6" width="54.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1094</v>
       </c>
@@ -7788,8 +8322,11 @@
       <c r="F1" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -7808,8 +8345,11 @@
       <c r="F2" t="s">
         <v>466</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -7828,8 +8368,11 @@
       <c r="F3" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -7848,8 +8391,11 @@
       <c r="F4" t="s">
         <v>476</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -7868,8 +8414,11 @@
       <c r="F5" t="s">
         <v>481</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -7888,8 +8437,11 @@
       <c r="F6" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -7908,8 +8460,11 @@
       <c r="F7" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -7928,8 +8483,11 @@
       <c r="F8" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -7948,8 +8506,11 @@
       <c r="F9" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -7968,8 +8529,11 @@
       <c r="F10" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -7988,8 +8552,11 @@
       <c r="F11" t="s">
         <v>510</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -8008,8 +8575,11 @@
       <c r="F12" t="s">
         <v>515</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -8028,8 +8598,11 @@
       <c r="F13" t="s">
         <v>519</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -8048,8 +8621,11 @@
       <c r="F14" t="s">
         <v>524</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>75</v>
       </c>
@@ -8068,8 +8644,11 @@
       <c r="F15" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -8088,8 +8667,11 @@
       <c r="F16" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -8108,8 +8690,11 @@
       <c r="F17" t="s">
         <v>537</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>93</v>
       </c>
@@ -8128,8 +8713,11 @@
       <c r="F18" t="s">
         <v>542</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -8148,8 +8736,11 @@
       <c r="F19" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -8168,8 +8759,11 @@
       <c r="F20" t="s">
         <v>549</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -8187,6 +8781,9 @@
       </c>
       <c r="F21" t="s">
         <v>554</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1117</v>
       </c>
     </row>
   </sheetData>
@@ -8200,7 +8797,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0C6A280-690C-49CB-BD7A-FB18F334D38E}">
   <sheetPr codeName="Sheet18"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -8211,7 +8808,7 @@
     <col min="6" max="6" width="54.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1094</v>
       </c>
@@ -8230,8 +8827,11 @@
       <c r="F1" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -8250,8 +8850,11 @@
       <c r="F2" t="s">
         <v>559</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -8270,8 +8873,11 @@
       <c r="F3" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -8290,8 +8896,11 @@
       <c r="F4" t="s">
         <v>1103</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -8310,8 +8919,11 @@
       <c r="F5" t="s">
         <v>570</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -8330,8 +8942,11 @@
       <c r="F6" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -8350,8 +8965,11 @@
       <c r="F7" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -8370,8 +8988,11 @@
       <c r="F8" t="s">
         <v>570</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -8390,8 +9011,11 @@
       <c r="F9" t="s">
         <v>589</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -8410,8 +9034,11 @@
       <c r="F10" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -8430,8 +9057,11 @@
       <c r="F11" t="s">
         <v>597</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -8450,8 +9080,11 @@
       <c r="F12" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -8470,8 +9103,11 @@
       <c r="F13" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -8490,8 +9126,11 @@
       <c r="F14" t="s">
         <v>612</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>75</v>
       </c>
@@ -8510,8 +9149,11 @@
       <c r="F15" t="s">
         <v>617</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -8530,8 +9172,11 @@
       <c r="F16" t="s">
         <v>622</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -8550,8 +9195,11 @@
       <c r="F17" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>93</v>
       </c>
@@ -8570,8 +9218,11 @@
       <c r="F18" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -8590,8 +9241,11 @@
       <c r="F19" t="s">
         <v>633</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -8610,8 +9264,11 @@
       <c r="F20" t="s">
         <v>638</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -8629,6 +9286,9 @@
       </c>
       <c r="F21" t="s">
         <v>641</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1117</v>
       </c>
     </row>
   </sheetData>
@@ -8642,7 +9302,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EA69202-F3D2-41E9-81E0-15032984F918}">
   <sheetPr codeName="Sheet17"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -8653,7 +9313,7 @@
     <col min="6" max="6" width="23.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1094</v>
       </c>
@@ -8672,8 +9332,11 @@
       <c r="F1" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -8692,8 +9355,11 @@
       <c r="F2" t="s">
         <v>646</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -8712,8 +9378,11 @@
       <c r="F3" t="s">
         <v>651</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -8732,8 +9401,11 @@
       <c r="F4" t="s">
         <v>656</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -8752,8 +9424,11 @@
       <c r="F5" t="s">
         <v>661</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -8772,8 +9447,11 @@
       <c r="F6" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -8792,8 +9470,11 @@
       <c r="F7" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -8812,8 +9493,11 @@
       <c r="F8" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -8832,8 +9516,11 @@
       <c r="F9" t="s">
         <v>680</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -8852,8 +9539,11 @@
       <c r="F10" t="s">
         <v>685</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -8872,8 +9562,11 @@
       <c r="F11" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -8892,8 +9585,11 @@
       <c r="F12" t="s">
         <v>695</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -8912,8 +9608,11 @@
       <c r="F13" t="s">
         <v>700</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -8932,8 +9631,11 @@
       <c r="F14" t="s">
         <v>650</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>75</v>
       </c>
@@ -8952,8 +9654,11 @@
       <c r="F15" t="s">
         <v>708</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -8972,8 +9677,11 @@
       <c r="F16" t="s">
         <v>713</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -8992,8 +9700,11 @@
       <c r="F17" t="s">
         <v>718</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>93</v>
       </c>
@@ -9012,8 +9723,11 @@
       <c r="F18" t="s">
         <v>723</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -9032,8 +9746,11 @@
       <c r="F19" t="s">
         <v>727</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -9052,8 +9769,11 @@
       <c r="F20" t="s">
         <v>732</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -9071,6 +9791,9 @@
       </c>
       <c r="F21" t="s">
         <v>737</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1117</v>
       </c>
     </row>
   </sheetData>
@@ -9084,7 +9807,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F9A0E2A-797F-41EB-8614-D31738EBBC00}">
   <sheetPr codeName="Sheet16"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -9094,7 +9817,7 @@
     <col min="6" max="6" width="27.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1094</v>
       </c>
@@ -9113,8 +9836,11 @@
       <c r="F1" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -9133,8 +9859,11 @@
       <c r="F2" t="s">
         <v>742</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -9153,8 +9882,11 @@
       <c r="F3" t="s">
         <v>747</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -9173,8 +9905,11 @@
       <c r="F4" t="s">
         <v>752</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -9193,8 +9928,11 @@
       <c r="F5" t="s">
         <v>757</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -9213,8 +9951,11 @@
       <c r="F6" t="s">
         <v>762</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -9233,8 +9974,11 @@
       <c r="F7" t="s">
         <v>767</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -9253,8 +9997,11 @@
       <c r="F8" t="s">
         <v>772</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -9273,8 +10020,11 @@
       <c r="F9" t="s">
         <v>776</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -9293,8 +10043,11 @@
       <c r="F10" t="s">
         <v>781</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -9313,8 +10066,11 @@
       <c r="F11" t="s">
         <v>786</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -9333,8 +10089,11 @@
       <c r="F12" t="s">
         <v>790</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -9353,8 +10112,11 @@
       <c r="F13" t="s">
         <v>795</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -9373,8 +10135,11 @@
       <c r="F14" t="s">
         <v>800</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>75</v>
       </c>
@@ -9393,8 +10158,11 @@
       <c r="F15" t="s">
         <v>805</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -9413,8 +10181,11 @@
       <c r="F16" t="s">
         <v>809</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -9433,8 +10204,11 @@
       <c r="F17" t="s">
         <v>814</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>93</v>
       </c>
@@ -9453,8 +10227,11 @@
       <c r="F18" t="s">
         <v>1107</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -9473,8 +10250,11 @@
       <c r="F19" t="s">
         <v>820</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -9493,8 +10273,11 @@
       <c r="F20" t="s">
         <v>825</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -9512,6 +10295,9 @@
       </c>
       <c r="F21" t="s">
         <v>830</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1117</v>
       </c>
     </row>
   </sheetData>

--- a/Data/OM/OM_Quizzes.xlsx
+++ b/Data/OM/OM_Quizzes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyCode\mba_quiz\Data\OM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46FFF869-3F88-4323-819B-93EC1385C00F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB11FF18-6881-4218-AC7D-2402F0FA71CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{850D3C83-EED4-4016-BDB5-EF8EECDCB418}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="4" activeTab="11" xr2:uid="{850D3C83-EED4-4016-BDB5-EF8EECDCB418}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="13" r:id="rId1"/>
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="1118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="1121">
   <si>
     <t xml:space="preserve">Question 1 </t>
   </si>
@@ -3459,6 +3459,15 @@
   </si>
   <si>
     <t>A</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
 </sst>
 </file>
@@ -3746,7 +3755,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{6DAA7E45-1438-48E4-BBD4-3FF9A64650B6}" name="Invoked_Function" displayName="Invoked_Function" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{6DAA7E45-1438-48E4-BBD4-3FF9A64650B6}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{4F4DC1AE-9891-4D2C-81CA-FF83A0666932}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{4F4DC1AE-9891-4D2C-81CA-FF83A0666932}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{3316EEB5-4012-4932-949C-59C1B8B3015E}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{F7253B9B-F333-458E-BEBB-53DA19583134}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{74EA87A1-A1E1-4D42-B81A-0036004754E0}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3762,7 +3771,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{435052D4-19AB-4E15-8BAC-29CC5B7F9B71}" name="Invoked_Function__10" displayName="Invoked_Function__10" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{435052D4-19AB-4E15-8BAC-29CC5B7F9B71}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{088F530A-F6B0-4576-8DAF-939017B752F3}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{088F530A-F6B0-4576-8DAF-939017B752F3}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{98FBB0FF-3819-418D-AE51-83B0880EA881}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{041B5EC7-E505-4A80-97E7-5D2D58BC4D57}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{5C0441B3-7FEC-4475-803C-74BE6EE3530C}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3778,7 +3787,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{2EFC25D6-673F-46F4-8772-BA41AC6386EF}" name="Invoked_Function__11" displayName="Invoked_Function__11" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{2EFC25D6-673F-46F4-8772-BA41AC6386EF}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{D5716560-84A7-4D1E-87A8-12FC230551F4}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{D5716560-84A7-4D1E-87A8-12FC230551F4}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{6DCE77D5-DFC2-4749-93EB-7E66318B6086}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{6C44B63C-AFA2-4A05-8864-468ECE1608C7}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{811FFC1A-E1FB-4C61-A29D-211B566B1358}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3794,7 +3803,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{54349323-E225-4000-80BB-229C42209659}" name="Invoked_Function__12" displayName="Invoked_Function__12" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{54349323-E225-4000-80BB-229C42209659}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{34D2D8E0-5D98-4E33-9B27-4EB54DF9D0DD}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{34D2D8E0-5D98-4E33-9B27-4EB54DF9D0DD}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{6D013BCE-29CA-480A-856D-4B77441E48A5}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{65878C6D-02B2-4718-8E1A-2EA522FAB55C}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{FCB25CD2-1B15-4356-AE5A-1C374BFC8E60}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3810,7 +3819,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{C3BA8602-D9EC-4CC6-8342-A610BF185308}" name="Invoked_Function__2" displayName="Invoked_Function__2" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{C3BA8602-D9EC-4CC6-8342-A610BF185308}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{FD297B3E-6F4E-4299-BC61-F59EB049387C}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{FD297B3E-6F4E-4299-BC61-F59EB049387C}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{08808285-7BB7-4B8E-B6A2-862AFC142B9D}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{8E1D4074-7785-4456-8080-9517A54670F4}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{DAABEC48-0663-457E-9A87-F652A956CBC8}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3826,7 +3835,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{3ABD55B9-6434-45DD-B30C-BEA19CF6D4E9}" name="Invoked_Function__3" displayName="Invoked_Function__3" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{3ABD55B9-6434-45DD-B30C-BEA19CF6D4E9}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{6ED9E7E7-904D-44A8-922A-0AE2929493CB}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{6ED9E7E7-904D-44A8-922A-0AE2929493CB}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{FFFA1420-5284-4BAA-BDB5-2419CBBC7713}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{B4B389E9-32FC-4116-AD66-165CF95D0CF5}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{71E5AE82-4D16-417D-BC33-5D8339BD7813}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3842,7 +3851,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{F391CFF9-11B6-4C6A-B49E-E899846B77FB}" name="Invoked_Function__4" displayName="Invoked_Function__4" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{F391CFF9-11B6-4C6A-B49E-E899846B77FB}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{6E57B712-A176-4715-93AA-F697952F56E8}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{6E57B712-A176-4715-93AA-F697952F56E8}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{2FFB4E15-CDF9-4C3B-8950-6C99A84E5DBF}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{E31F55BB-5175-425B-9F71-96B4049ABBD7}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{6A1D1FF4-DC71-4C35-82EC-9C40D5D74293}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3858,7 +3867,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{0B336DAA-9B7B-4435-8098-7BE4D3C2A28B}" name="Invoked_Function__5" displayName="Invoked_Function__5" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{0B336DAA-9B7B-4435-8098-7BE4D3C2A28B}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{6F04D2E1-D13A-4CCE-BC1C-2683E408F03A}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{6F04D2E1-D13A-4CCE-BC1C-2683E408F03A}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{76CE457E-A45B-4F93-A927-93D8237A9E97}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{F6D6C614-E9E1-4658-A7BE-C0656F92C0EB}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{21D96AD7-C064-4EBE-A1BC-88EFADE23288}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3874,7 +3883,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{976449B6-5F63-4BCD-ADE8-D8DB40B8FA4C}" name="Invoked_Function__6" displayName="Invoked_Function__6" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{976449B6-5F63-4BCD-ADE8-D8DB40B8FA4C}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{145C51E1-C78B-47CB-A5AC-DDA65C8E18A2}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{145C51E1-C78B-47CB-A5AC-DDA65C8E18A2}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{E51CC0F5-CCB1-472B-BD8C-7D6D83E4CF15}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{D195B80E-4918-401A-B38D-F722EFAFE08F}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{4D3E205A-4061-4184-85E4-520B5613029F}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3890,7 +3899,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{6C35EC66-EE0E-4044-BDBC-3336C63ABAA5}" name="Invoked_Function__7" displayName="Invoked_Function__7" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{6C35EC66-EE0E-4044-BDBC-3336C63ABAA5}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{204FFCFE-E32A-4180-A147-D0D393037A11}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{204FFCFE-E32A-4180-A147-D0D393037A11}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{2117BA69-A095-45E8-85BC-A8FF775648B7}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{E33BD793-75DE-4B42-B115-CFC63E7EA719}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{FEBB3995-9725-44AA-81F2-F9F10A434981}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3906,7 +3915,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{58941E16-4E46-41BD-B8E1-D1E32BB562A5}" name="Invoked_Function__8" displayName="Invoked_Function__8" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{58941E16-4E46-41BD-B8E1-D1E32BB562A5}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{985D7F0A-A4BA-43C5-A78F-3ECA5F83658D}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{985D7F0A-A4BA-43C5-A78F-3ECA5F83658D}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{E44469FE-6E9E-4B34-86C1-1E0F50A5BB56}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{C056C849-CF48-45C1-8A39-78AB9AA074F7}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{DAA2F508-B0CD-422E-BC72-CA367389D287}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3922,7 +3931,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{20220D49-688A-4E6F-B076-C476A008EA2E}" name="Invoked_Function__9" displayName="Invoked_Function__9" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{20220D49-688A-4E6F-B076-C476A008EA2E}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{9CBF8650-ACEB-4018-BE8E-BBA77FDBEDB5}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{9CBF8650-ACEB-4018-BE8E-BBA77FDBEDB5}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{DFF65E6F-2820-4C06-BF88-2E5AEA27798D}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{2DA3D069-C9DB-4141-AAC7-0DD1B471C96D}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{E692B638-331D-4457-A25B-4FCECAF8D4C0}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -4329,7 +4338,7 @@
         <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -4352,7 +4361,7 @@
         <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -4375,7 +4384,7 @@
         <v>23</v>
       </c>
       <c r="G5" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -4398,7 +4407,7 @@
         <v>29</v>
       </c>
       <c r="G6" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -4421,7 +4430,7 @@
         <v>35</v>
       </c>
       <c r="G7" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -4444,7 +4453,7 @@
         <v>41</v>
       </c>
       <c r="G8" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -4467,7 +4476,7 @@
         <v>47</v>
       </c>
       <c r="G9" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -4490,7 +4499,7 @@
         <v>51</v>
       </c>
       <c r="G10" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -4513,7 +4522,7 @@
         <v>57</v>
       </c>
       <c r="G11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -4559,7 +4568,7 @@
         <v>69</v>
       </c>
       <c r="G13" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -4582,7 +4591,7 @@
         <v>74</v>
       </c>
       <c r="G14" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -4605,7 +4614,7 @@
         <v>80</v>
       </c>
       <c r="G15" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -4628,7 +4637,7 @@
         <v>86</v>
       </c>
       <c r="G16" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -4651,7 +4660,7 @@
         <v>92</v>
       </c>
       <c r="G17" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -4697,7 +4706,7 @@
         <v>103</v>
       </c>
       <c r="G19" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -4720,7 +4729,7 @@
         <v>109</v>
       </c>
       <c r="G20" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -4811,7 +4820,7 @@
         <v>835</v>
       </c>
       <c r="G2" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -4834,7 +4843,7 @@
         <v>840</v>
       </c>
       <c r="G3" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -4857,7 +4866,7 @@
         <v>845</v>
       </c>
       <c r="G4" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -4880,7 +4889,7 @@
         <v>850</v>
       </c>
       <c r="G5" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -4903,7 +4912,7 @@
         <v>855</v>
       </c>
       <c r="G6" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -4926,7 +4935,7 @@
         <v>860</v>
       </c>
       <c r="G7" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -4949,7 +4958,7 @@
         <v>865</v>
       </c>
       <c r="G8" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -4972,7 +4981,7 @@
         <v>870</v>
       </c>
       <c r="G9" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -4995,7 +5004,7 @@
         <v>875</v>
       </c>
       <c r="G10" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -5041,7 +5050,7 @@
         <v>885</v>
       </c>
       <c r="G12" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -5087,7 +5096,7 @@
         <v>895</v>
       </c>
       <c r="G14" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -5133,7 +5142,7 @@
         <v>905</v>
       </c>
       <c r="G16" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -5202,7 +5211,7 @@
         <v>920</v>
       </c>
       <c r="G19" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -5225,7 +5234,7 @@
         <v>879</v>
       </c>
       <c r="G20" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -5316,7 +5325,7 @@
         <v>930</v>
       </c>
       <c r="G2" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -5339,7 +5348,7 @@
         <v>934</v>
       </c>
       <c r="G3" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -5362,7 +5371,7 @@
         <v>938</v>
       </c>
       <c r="G4" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -5385,7 +5394,7 @@
         <v>942</v>
       </c>
       <c r="G5" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -5454,7 +5463,7 @@
         <v>954</v>
       </c>
       <c r="G8" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -5477,7 +5486,7 @@
         <v>959</v>
       </c>
       <c r="G9" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -5500,7 +5509,7 @@
         <v>964</v>
       </c>
       <c r="G10" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -5523,7 +5532,7 @@
         <v>969</v>
       </c>
       <c r="G11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -5569,7 +5578,7 @@
         <v>978</v>
       </c>
       <c r="G13" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -5615,7 +5624,7 @@
         <v>987</v>
       </c>
       <c r="G15" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -5638,7 +5647,7 @@
         <v>992</v>
       </c>
       <c r="G16" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -5684,7 +5693,7 @@
         <v>1109</v>
       </c>
       <c r="G18" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -5707,7 +5716,7 @@
         <v>1004</v>
       </c>
       <c r="G19" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -5730,7 +5739,7 @@
         <v>1009</v>
       </c>
       <c r="G20" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -5753,7 +5762,7 @@
         <v>1014</v>
       </c>
       <c r="G21" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
   </sheetData>
@@ -5821,7 +5830,7 @@
         <v>1018</v>
       </c>
       <c r="G2" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -5844,7 +5853,7 @@
         <v>1023</v>
       </c>
       <c r="G3" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -5867,7 +5876,7 @@
         <v>1028</v>
       </c>
       <c r="G4" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -5890,7 +5899,7 @@
         <v>1033</v>
       </c>
       <c r="G5" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -5913,7 +5922,7 @@
         <v>1038</v>
       </c>
       <c r="G6" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -5936,7 +5945,7 @@
         <v>1043</v>
       </c>
       <c r="G7" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -5959,7 +5968,7 @@
         <v>1048</v>
       </c>
       <c r="G8" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -6005,7 +6014,7 @@
         <v>1054</v>
       </c>
       <c r="G10" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -6028,7 +6037,7 @@
         <v>1059</v>
       </c>
       <c r="G11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -6051,7 +6060,7 @@
         <v>1064</v>
       </c>
       <c r="G12" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -6074,7 +6083,7 @@
         <v>1069</v>
       </c>
       <c r="G13" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -6097,7 +6106,7 @@
         <v>1028</v>
       </c>
       <c r="G14" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -6120,7 +6129,7 @@
         <v>1075</v>
       </c>
       <c r="G15" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -6143,7 +6152,7 @@
         <v>1080</v>
       </c>
       <c r="G16" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -6166,7 +6175,7 @@
         <v>1021</v>
       </c>
       <c r="G17" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -6189,7 +6198,7 @@
         <v>1053</v>
       </c>
       <c r="G18" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -6212,7 +6221,7 @@
         <v>1089</v>
       </c>
       <c r="G19" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -6326,7 +6335,7 @@
         <v>119</v>
       </c>
       <c r="G2" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -6349,7 +6358,7 @@
         <v>124</v>
       </c>
       <c r="G3" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -6372,7 +6381,7 @@
         <v>127</v>
       </c>
       <c r="G4" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -6395,7 +6404,7 @@
         <v>132</v>
       </c>
       <c r="G5" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -6418,7 +6427,7 @@
         <v>136</v>
       </c>
       <c r="G6" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -6441,7 +6450,7 @@
         <v>140</v>
       </c>
       <c r="G7" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -6487,7 +6496,7 @@
         <v>150</v>
       </c>
       <c r="G9" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -6510,7 +6519,7 @@
         <v>130</v>
       </c>
       <c r="G10" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -6533,7 +6542,7 @@
         <v>156</v>
       </c>
       <c r="G11" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -6556,7 +6565,7 @@
         <v>161</v>
       </c>
       <c r="G12" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -6648,7 +6657,7 @@
         <v>178</v>
       </c>
       <c r="G16" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -6671,7 +6680,7 @@
         <v>180</v>
       </c>
       <c r="G17" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -6717,7 +6726,7 @@
         <v>188</v>
       </c>
       <c r="G19" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -6740,7 +6749,7 @@
         <v>1113</v>
       </c>
       <c r="G20" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -6854,7 +6863,7 @@
         <v>123</v>
       </c>
       <c r="G3" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -6877,7 +6886,7 @@
         <v>204</v>
       </c>
       <c r="G4" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -6900,7 +6909,7 @@
         <v>208</v>
       </c>
       <c r="G5" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -6923,7 +6932,7 @@
         <v>213</v>
       </c>
       <c r="G6" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -6946,7 +6955,7 @@
         <v>217</v>
       </c>
       <c r="G7" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -6992,7 +7001,7 @@
         <v>227</v>
       </c>
       <c r="G9" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -7038,7 +7047,7 @@
         <v>236</v>
       </c>
       <c r="G11" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -7061,7 +7070,7 @@
         <v>241</v>
       </c>
       <c r="G12" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -7084,7 +7093,7 @@
         <v>246</v>
       </c>
       <c r="G13" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -7107,7 +7116,7 @@
         <v>251</v>
       </c>
       <c r="G14" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -7130,7 +7139,7 @@
         <v>256</v>
       </c>
       <c r="G15" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -7153,7 +7162,7 @@
         <v>260</v>
       </c>
       <c r="G16" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -7176,7 +7185,7 @@
         <v>265</v>
       </c>
       <c r="G17" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -7245,7 +7254,7 @@
         <v>276</v>
       </c>
       <c r="G20" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -7268,7 +7277,7 @@
         <v>281</v>
       </c>
       <c r="G21" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
   </sheetData>
@@ -7336,7 +7345,7 @@
         <v>286</v>
       </c>
       <c r="G2" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -7382,7 +7391,7 @@
         <v>296</v>
       </c>
       <c r="G4" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -7405,7 +7414,7 @@
         <v>301</v>
       </c>
       <c r="G5" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -7428,7 +7437,7 @@
         <v>306</v>
       </c>
       <c r="G6" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -7474,7 +7483,7 @@
         <v>316</v>
       </c>
       <c r="G8" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -7497,7 +7506,7 @@
         <v>321</v>
       </c>
       <c r="G9" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -7520,7 +7529,7 @@
         <v>326</v>
       </c>
       <c r="G10" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -7543,7 +7552,7 @@
         <v>330</v>
       </c>
       <c r="G11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -7566,7 +7575,7 @@
         <v>335</v>
       </c>
       <c r="G12" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -7589,7 +7598,7 @@
         <v>340</v>
       </c>
       <c r="G13" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -7612,7 +7621,7 @@
         <v>344</v>
       </c>
       <c r="G14" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -7635,7 +7644,7 @@
         <v>349</v>
       </c>
       <c r="G15" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -7658,7 +7667,7 @@
         <v>354</v>
       </c>
       <c r="G16" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -7681,7 +7690,7 @@
         <v>332</v>
       </c>
       <c r="G17" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -7727,7 +7736,7 @@
         <v>363</v>
       </c>
       <c r="G19" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -7750,7 +7759,7 @@
         <v>332</v>
       </c>
       <c r="G20" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -7773,7 +7782,7 @@
         <v>356</v>
       </c>
       <c r="G21" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
   </sheetData>
@@ -7864,7 +7873,7 @@
         <v>376</v>
       </c>
       <c r="G3" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -7887,7 +7896,7 @@
         <v>381</v>
       </c>
       <c r="G4" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -7910,7 +7919,7 @@
         <v>386</v>
       </c>
       <c r="G5" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -7933,7 +7942,7 @@
         <v>391</v>
       </c>
       <c r="G6" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -8025,7 +8034,7 @@
         <v>410</v>
       </c>
       <c r="G10" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -8048,7 +8057,7 @@
         <v>415</v>
       </c>
       <c r="G11" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -8071,7 +8080,7 @@
         <v>420</v>
       </c>
       <c r="G12" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -8094,7 +8103,7 @@
         <v>425</v>
       </c>
       <c r="G13" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -8117,7 +8126,7 @@
         <v>430</v>
       </c>
       <c r="G14" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -8140,7 +8149,7 @@
         <v>435</v>
       </c>
       <c r="G15" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -8163,7 +8172,7 @@
         <v>440</v>
       </c>
       <c r="G16" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -8209,7 +8218,7 @@
         <v>449</v>
       </c>
       <c r="G18" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -8255,7 +8264,7 @@
         <v>459</v>
       </c>
       <c r="G20" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -8278,7 +8287,7 @@
         <v>457</v>
       </c>
       <c r="G21" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
   </sheetData>
@@ -8346,7 +8355,7 @@
         <v>466</v>
       </c>
       <c r="G2" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -8369,7 +8378,7 @@
         <v>471</v>
       </c>
       <c r="G3" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -8392,7 +8401,7 @@
         <v>476</v>
       </c>
       <c r="G4" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -8415,7 +8424,7 @@
         <v>481</v>
       </c>
       <c r="G5" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -8438,7 +8447,7 @@
         <v>486</v>
       </c>
       <c r="G6" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -8461,7 +8470,7 @@
         <v>491</v>
       </c>
       <c r="G7" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -8484,7 +8493,7 @@
         <v>496</v>
       </c>
       <c r="G8" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -8507,7 +8516,7 @@
         <v>501</v>
       </c>
       <c r="G9" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -8530,7 +8539,7 @@
         <v>376</v>
       </c>
       <c r="G10" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -8553,7 +8562,7 @@
         <v>510</v>
       </c>
       <c r="G11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -8576,7 +8585,7 @@
         <v>515</v>
       </c>
       <c r="G12" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -8622,7 +8631,7 @@
         <v>524</v>
       </c>
       <c r="G14" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -8645,7 +8654,7 @@
         <v>527</v>
       </c>
       <c r="G15" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -8668,7 +8677,7 @@
         <v>532</v>
       </c>
       <c r="G16" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -8691,7 +8700,7 @@
         <v>537</v>
       </c>
       <c r="G17" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -8714,7 +8723,7 @@
         <v>542</v>
       </c>
       <c r="G18" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -8760,7 +8769,7 @@
         <v>549</v>
       </c>
       <c r="G20" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -8783,7 +8792,7 @@
         <v>554</v>
       </c>
       <c r="G21" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
   </sheetData>
@@ -8874,7 +8883,7 @@
         <v>564</v>
       </c>
       <c r="G3" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -8897,7 +8906,7 @@
         <v>1103</v>
       </c>
       <c r="G4" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -8943,7 +8952,7 @@
         <v>575</v>
       </c>
       <c r="G6" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -8966,7 +8975,7 @@
         <v>580</v>
       </c>
       <c r="G7" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -9012,7 +9021,7 @@
         <v>589</v>
       </c>
       <c r="G9" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -9058,7 +9067,7 @@
         <v>597</v>
       </c>
       <c r="G11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -9081,7 +9090,7 @@
         <v>602</v>
       </c>
       <c r="G12" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -9127,7 +9136,7 @@
         <v>612</v>
       </c>
       <c r="G14" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -9150,7 +9159,7 @@
         <v>617</v>
       </c>
       <c r="G15" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -9173,7 +9182,7 @@
         <v>622</v>
       </c>
       <c r="G16" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -9219,7 +9228,7 @@
         <v>602</v>
       </c>
       <c r="G18" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -9242,7 +9251,7 @@
         <v>633</v>
       </c>
       <c r="G19" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -9356,7 +9365,7 @@
         <v>646</v>
       </c>
       <c r="G2" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -9379,7 +9388,7 @@
         <v>651</v>
       </c>
       <c r="G3" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -9425,7 +9434,7 @@
         <v>661</v>
       </c>
       <c r="G5" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -9448,7 +9457,7 @@
         <v>666</v>
       </c>
       <c r="G6" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -9494,7 +9503,7 @@
         <v>675</v>
       </c>
       <c r="G8" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -9517,7 +9526,7 @@
         <v>680</v>
       </c>
       <c r="G9" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -9540,7 +9549,7 @@
         <v>685</v>
       </c>
       <c r="G10" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -9563,7 +9572,7 @@
         <v>690</v>
       </c>
       <c r="G11" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -9586,7 +9595,7 @@
         <v>695</v>
       </c>
       <c r="G12" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -9655,7 +9664,7 @@
         <v>708</v>
       </c>
       <c r="G15" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -9678,7 +9687,7 @@
         <v>713</v>
       </c>
       <c r="G16" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -9701,7 +9710,7 @@
         <v>718</v>
       </c>
       <c r="G17" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -9770,7 +9779,7 @@
         <v>732</v>
       </c>
       <c r="G20" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -9793,7 +9802,7 @@
         <v>737</v>
       </c>
       <c r="G21" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
   </sheetData>
@@ -9860,7 +9869,7 @@
         <v>742</v>
       </c>
       <c r="G2" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -9883,7 +9892,7 @@
         <v>747</v>
       </c>
       <c r="G3" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -9906,7 +9915,7 @@
         <v>752</v>
       </c>
       <c r="G4" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -9929,7 +9938,7 @@
         <v>757</v>
       </c>
       <c r="G5" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -9952,7 +9961,7 @@
         <v>762</v>
       </c>
       <c r="G6" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -9975,7 +9984,7 @@
         <v>767</v>
       </c>
       <c r="G7" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -10021,7 +10030,7 @@
         <v>776</v>
       </c>
       <c r="G9" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -10090,7 +10099,7 @@
         <v>790</v>
       </c>
       <c r="G12" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -10136,7 +10145,7 @@
         <v>800</v>
       </c>
       <c r="G14" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -10159,7 +10168,7 @@
         <v>805</v>
       </c>
       <c r="G15" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -10274,7 +10283,7 @@
         <v>825</v>
       </c>
       <c r="G20" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
